--- a/testdata/fixtures/members_missing_email.xlsx
+++ b/testdata/fixtures/members_missing_email.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">Liste des membres Club de plongée d'exemple</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t xml:space="preserve">Année(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organisation</t>
   </si>
   <si>
     <t xml:space="preserve">31/12/2026</t>
@@ -203,58 +206,61 @@
       <c r="W4" t="s">
         <v>20</v>
       </c>
+      <c r="X4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q5" t="s">
+        <v>33</v>
+      </c>
+      <c r="R5" t="s">
+        <v>34</v>
+      </c>
+      <c r="S5" t="s">
+        <v>35</v>
+      </c>
+      <c r="U5" t="s">
         <v>32</v>
       </c>
-      <c r="R5" t="s">
-        <v>33</v>
-      </c>
-      <c r="S5" t="s">
-        <v>34</v>
-      </c>
-      <c r="U5" t="s">
-        <v>31</v>
-      </c>
       <c r="V5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="W5">
         <v>2026</v>
